--- a/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Baptiste a faim. La soupe sent le potiron. Papa pose les assiettes sur la table. Maman dit : on mange assis. Ensemble. Baptiste pose ses fesses sur la chaise. Il est assis. Parce qu'il est assis, la cuillère reste calme. Papa s'assoit. Maman s'assoit. Ils mangent ensemble à table. Baptiste sent le chaud. Il dit : on est assis. Ensemble. À table. La soupe est douce. Maman sourit.</t>
+          <t>Baptiste a faim. La soupe sent le potiron. Papa pose les assiettes sur la table. On mange assis. Ensemble. Baptiste pose ses fesses sur la chaise. Il est assis. Parce qu'il est assis, la cuillère reste calme. Papa s'assoit. Maman s'assoit. Ils mangent ensemble à table. Baptiste sent le chaud. On est assis. Ensemble. À table. La soupe est douce. Maman sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste a faim. La soupe sent le potiron. Papa pose les assiettes sur la table.
+maman|On mange assis. Ensemble.
+narrateur|Baptiste pose ses fesses sur la chaise. Il est assis. Parce qu'il est assis, la cuillère reste calme. Papa s'assoit. Maman s'assoit. Ils mangent ensemble à table. Baptiste sent le chaud.
+narrateur|On est assis. Ensemble. À table.
+narrateur|La soupe est douce. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste mange. Où est-il, et comment ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste s'est assis. Il a mangé à table. Papa et maman étaient ensemble avec lui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste pose sa cuillère. Il dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|La soupe est douce. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Baptiste mange. Où est-il, et comment ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Baptiste s'est assis. Il a mangé à table. Papa et maman étaient ensemble avec lui.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Baptiste pose sa cuillère. Il dit merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Baptiste s'assoit à table</t>
+          <t>Le torchon orange</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un torchon orange sèche près de la fenêtre. La casserole a un ventre rond. Sarah amène sa chaise. On mange assis, ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Baptiste a faim. La soupe sent le potiron. Papa pose les assiettes sur la table. On mange assis. Ensemble. Baptiste pose ses fesses sur la chaise. Il est assis. Parce qu'il est assis, la cuillère reste calme. Papa s'assoit. Maman s'assoit. Ils mangent ensemble à table. Baptiste sent le chaud. On est assis. Ensemble. À table. La soupe est douce. Maman sourit.</t>
+          <t>Un torchon orange sèche près de la fenêtre. Il bouge un peu, tout doux. Dehors, le soir arrive, tout rose. La casserole a un ventre rond. Ça sent le potiron. Une petite fumée danse au-dessus. Sarah habite ici, avec papa et maman. Ses chaussettes sont épaisses, un peu grises. Le carrelage est tiède encore. Ça sent le potiron, maman ! Oui, Sarah. La soupe est presque prête. J'apporte les assiettes. Les assiettes font un petit bruit. Le pain est dans le panier. En ce moment, Sarah a faim. Sarah, viens. On va à table. Viens t'asseoir. Sarah va vers sa chaise. Elle tire un peu la chaise. Elle s'assoit. Elle pose les pieds par terre. Bravo, Sarah. Tu es bien assise. Papa s'assoit aussi. Maman s'assoit près d'elle. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Elle pose les mains. La table est un peu chaude. Tu as vu la petite fumée ? Elle danse encore. On attend un petit moment. Sarah tient sa cuillère. Elle reste assise. Tu as vu le torchon orange ? Il sèche, maman. Oui. Il sèche près de nous. La soupe fume tout près. Ça sent bon, hein ? Ça sent le potiron. Tu restes bien assise ? Oui, papa. Bravo. Le pain attend dans le panier. On mange assis. Ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste a faim. La soupe sent le potiron. Papa pose les assiettes sur la table.
-maman|On mange assis. Ensemble.
-narrateur|Baptiste pose ses fesses sur la chaise. Il est assis. Parce qu'il est assis, la cuillère reste calme. Papa s'assoit. Maman s'assoit. Ils mangent ensemble à table. Baptiste sent le chaud.
-narrateur|On est assis. Ensemble. À table.
-narrateur|La soupe est douce. Maman sourit.</t>
+          <t>narrateur|Un torchon orange sèche près de la fenêtre.
+narrateur|Il bouge un peu, tout doux.
+narrateur|Dehors, le soir arrive, tout rose.
+narrateur|La casserole a un ventre rond.
+narrateur|Ça sent le potiron.
+narrateur|Une petite fumée danse au-dessus.
+narrateur|Sarah habite ici, avec papa et maman.
+narrateur|Ses chaussettes sont épaisses, un peu grises.
+narrateur|Le carrelage est tiède encore.
+enfant-f|Ça sent le potiron, maman !
+maman|Oui, Sarah.
+maman|La soupe est presque prête.
+papa|J'apporte les assiettes.
+narrateur|Les assiettes font un petit bruit.
+narrateur|Le pain est dans le panier.
+narrateur|En ce moment, Sarah a faim.
+papa|Sarah, viens.
+papa|On va à table.
+maman|Viens t'asseoir.
+narrateur|Sarah va vers sa chaise.
+narrateur|Elle tire un peu la chaise.
+narrateur|Elle s'assoit.
+narrateur|Elle pose les pieds par terre.
+papa|Bravo, Sarah.
+papa|Tu es bien assise.
+narrateur|Papa s'assoit aussi.
+narrateur|Maman s'assoit près d'elle.
+maman|On est ensemble.
+maman|On mange à table.
+narrateur|Sa chaise ne bouge plus.
+papa|Tu poses les mains sur la table ?
+narrateur|Elle pose les mains.
+narrateur|La table est un peu chaude.
+maman|Tu as vu la petite fumée ?
+enfant-f|Elle danse encore.
+papa|On attend un petit moment.
+narrateur|Sarah tient sa cuillère.
+narrateur|Elle reste assise.
+maman|Tu as vu le torchon orange ?
+enfant-f|Il sèche, maman.
+papa|Oui.
+papa|Il sèche près de nous.
+narrateur|La soupe fume tout près.
+maman|Ça sent bon, hein ?
+enfant-f|Ça sent le potiron.
+papa|Tu restes bien assise ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Le pain attend dans le panier.
+maman|On mange assis.
+maman|Ensemble.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>casserole,chaise</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Baptiste mange. Où est-il, et comment ?</t>
+          <t>Sarah mange. Où est-elle, et comment ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste mange. Où est-il, et comment ?</t>
+          <t>narrateur|Sarah mange.
+narrateur|Où est-elle, et comment ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Baptiste s'est assis. Il a mangé à table. Papa et maman étaient ensemble avec lui.</t>
+          <t>Sarah est assise. Elle est à table. On est tous assis. On est ensemble. La soupe attend. Ta chaise reste à table ? Oui. Sarah reste assise. Le torchon orange écoute, tout sage. Il sèche avec nous ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1740,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste s'est assis. Il a mangé à table. Papa et maman étaient ensemble avec lui.</t>
+          <t>narrateur|Sarah est assise.
+narrateur|Elle est à table.
+papa|On est tous assis.
+maman|On est ensemble.
+narrateur|La soupe attend.
+papa|Ta chaise reste à table ?
+enfant-f|Oui.
+narrateur|Sarah reste assise.
+narrateur|Le torchon orange écoute, tout sage.
+maman|Il sèche avec nous ?
+enfant-f|Oui.
+maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Baptiste pose sa cuillère. Il dit merci.</t>
+          <t>Papa coupe le pain. Le pain croustille. Tu prends ta cuillère ? Sarah prend sa cuillère. Tu attends un peu. C'est chaud. Elle attend un peu. Elle goûte. C'est chaud. C'est doux. Bravo, Sarah. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Sarah. Ils mangent ensemble. Sarah reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Sarah. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1915,30 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste pose sa cuillère. Il dit merci.</t>
+          <t>narrateur|Papa coupe le pain.
+narrateur|Le pain croustille.
+maman|Tu prends ta cuillère ?
+narrateur|Sarah prend sa cuillère.
+papa|Tu attends un peu. C'est chaud.
+narrateur|Elle attend un peu.
+narrateur|Elle goûte.
+enfant-f|C'est chaud.
+enfant-f|C'est doux.
+maman|Bravo, Sarah.
+maman|Tu as goûté.
+maman|C'est du bon travail.
+papa|Bon appétit.
+maman|Bon appétit, Sarah.
+narrateur|Ils mangent ensemble.
+narrateur|Sarah reste assise.
+papa|Encore une petite cuillère ?
+narrateur|Encore une cuillère.
+papa|Tu restes assise. Bravo.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+maman|Merci, Sarah.
+narrateur|Elle boit une gorgée.
+narrateur|Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La fumée s'en va. Le torchon orange ne bouge plus. On a mangé assis, ensemble. C'était doux. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2106,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La fumée s'en va.
+narrateur|Le torchon orange ne bouge plus.
+papa|On a mangé assis, ensemble.
+enfant-f|C'était doux.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2172,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Baptiste a faim. La soupe sent le potiron. Papa pose les assiettes sur la table. Maman dit : on mange &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Ensemble. Baptiste pose ses fesses sur la chaise. Il est assis. Parce qu'il est assis, la cuillère reste calme. Papa s'assoit. Maman s'assoit. Ils mangent ensemble à table. Baptiste sent le chaud. Il dit : on est assis. Ensemble. À table. La soupe est douce. Maman sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un torchon orange sèche près de la fenêtre. Il bouge un peu, tout doux. Dehors, le soir arrive, tout rose. La casserole a un ventre rond. Ça sent le potiron. Une petite fumée danse au-dessus. Sarah habite ici, avec papa et maman. Ses chaussettes sont épaisses, un peu grises. Le carrelage est tiède encore. Ça sent le potiron, maman ! Oui, Sarah. La soupe est presque prête. J'apporte les assiettes. Les assiettes font un petit bruit. Le pain est dans le panier. En ce moment, Sarah a faim. Sarah, viens. On va à table. Viens t'asseoir. Sarah va vers sa chaise. Elle tire un peu la chaise. Elle s'assoit. Elle pose les pieds par terre. Bravo, Sarah. Tu es bien assise. Papa s'assoit aussi. Maman s'assoit près d'elle. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Elle pose les mains. La table est un peu chaude. Tu as vu la petite fumée ? Elle danse encore. On attend un petit moment. Sarah tient sa cuillère. Elle reste assise. Tu as vu le torchon orange ? Il sèche, maman. Oui. Il sèche près de nous. La soupe fume tout près. Ça sent bon, hein ? Ça sent le potiron. Tu restes bien assise ? Oui, papa. Bravo. Le pain attend dans le panier. On mange assis. Ensemble.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sarah mange. Où est-elle, et comment ?</t>
+          <t>La soupe attend. Sarah est où ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Baptiste mange. Où est-il, et comment ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La soupe attend. Sarah est où ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1567,11 +1567,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sarah mange.
-narrateur|Où est-elle, et comment ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La soupe attend.
+narrateur|Sarah est où ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Baptiste s'est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Il a mangé à table. Papa et maman étaient ensemble avec lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah est assise. Elle est à table. On est tous assis. On est ensemble. La soupe attend. Ta chaise reste à table ? Oui. Sarah reste assise. Le torchon orange écoute, tout sage. Il sèche avec nous ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,7 +1753,6 @@
 maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1779,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa coupe le pain. Le pain croustille. Tu prends ta cuillère ? Sarah prend sa cuillère. Tu attends un peu. C'est chaud. Elle attend un peu. Elle goûte. C'est chaud. C'est doux. Bravo, Sarah. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Sarah. Ils mangent ensemble. Sarah reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Sarah. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
+          <t>Papa coupe le pain. Le pain croustille. Tu prends ta cuillère ? Sarah prend sa cuillère. Tu attends un peu. C'est chaud. Elle attend un peu. Elle goûte. C'est chaud. C'est doux. Bravo, Sarah. Tu as goûté. Bon appétit. Bon appétit, Sarah. Ils mangent ensemble. Sarah reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Sarah. Elle boit une gorgée. Elle reste assise jusqu'à la fin. Tu as fini ta soupe ? Un peu. Une petite portion, c'est assez. Tu restes à table avec nous ? Oui, papa. Bravo. Le torchon orange ne bouge plus. La casserole se repose.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Baptiste pose sa cuillère. Il dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa coupe le pain. Le pain croustille. Tu prends ta cuillère ? Sarah prend sa cuillère. Tu attends un peu. C'est chaud. Elle attend un peu. Elle goûte. C'est chaud. C'est doux. Bravo, Sarah. Tu as goûté. Bon appétit. Bon appétit, Sarah. Ils mangent ensemble. Sarah reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Sarah. Elle boit une gorgée. Elle reste assise jusqu'à la fin. Tu as fini ta soupe ? Un peu. Une petite portion, c'est assez. Tu restes à table avec nous ? Oui, papa. Bravo. Le torchon orange ne bouge plus. La casserole se repose.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,7 +1924,6 @@
 enfant-f|C'est doux.
 maman|Bravo, Sarah.
 maman|Tu as goûté.
-maman|C'est du bon travail.
 papa|Bon appétit.
 maman|Bon appétit, Sarah.
 narrateur|Ils mangent ensemble.
@@ -1938,10 +1935,17 @@
 enfant-f|Merci, papa.
 maman|Merci, Sarah.
 narrateur|Elle boit une gorgée.
-narrateur|Elle reste assise jusqu'à la fin.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|Elle reste assise jusqu'à la fin.
+maman|Tu as fini ta soupe ?
+enfant-f|Un peu.
+maman|Une petite portion, c'est assez.
+papa|Tu restes à table avec nous ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Le torchon orange ne bouge plus.
+narrateur|La casserole se repose.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1966,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La fumée s'en va. Le torchon orange ne bouge plus. On a mangé assis, ensemble. C'était doux. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>La fumée s'en va. Le torchon orange ne bouge plus. On a mangé assis, ensemble. C'était doux. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fumée s'en va. Le torchon orange ne bouge plus. On a mangé assis, ensemble. C'était doux. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2110,12 +2114,9 @@
 narrateur|Le torchon orange ne bouge plus.
 papa|On a mangé assis, ensemble.
 enfant-f|C'était doux.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2134,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2179,6 +2180,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-07.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baptiste, papa, maman</t>
+          <t>Sarah, papa, maman</t>
         </is>
       </c>
     </row>
